--- a/artfynd/A 61954-2025 artfynd.xlsx
+++ b/artfynd/A 61954-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111836217</v>
+        <v>111836214</v>
       </c>
       <c r="B2" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598585</v>
+        <v>598575</v>
       </c>
       <c r="R2" t="n">
-        <v>6981398</v>
+        <v>6981230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -780,16 +775,11 @@
         <v>111836215</v>
       </c>
       <c r="B3" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -820,7 +810,7 @@
         <v>598566</v>
       </c>
       <c r="R3" t="n">
-        <v>6981295</v>
+        <v>6981294</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,49 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111836214</v>
+        <v>111836216</v>
       </c>
       <c r="B4" t="n">
-        <v>90087</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598575</v>
+        <v>598566</v>
       </c>
       <c r="R4" t="n">
-        <v>6981231</v>
+        <v>6981294</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111836216</v>
+        <v>111836217</v>
       </c>
       <c r="B5" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598566</v>
+        <v>598585</v>
       </c>
       <c r="R5" t="n">
-        <v>6981295</v>
+        <v>6981397</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 61954-2025 artfynd.xlsx
+++ b/artfynd/A 61954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836214</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836215</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836216</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836217</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>